--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484621_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484621_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.338800000000001</v>
+        <v>9.684799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>10.6993</v>
+        <v>11.194</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3605</v>
+        <v>-1.5092</v>
       </c>
       <c r="G2" t="n">
         <v>5.4427</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3413</v>
+        <v>0.6874</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0746</v>
+        <v>0.4201</v>
       </c>
       <c r="U2" t="n">
-        <v>0.416</v>
+        <v>0.2673</v>
       </c>
       <c r="V2" t="n">
         <v>3.1882</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.345</v>
+        <v>5.7602</v>
       </c>
       <c r="E3" t="n">
-        <v>9.318199999999999</v>
+        <v>8.6591</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9732</v>
+        <v>-2.8989</v>
       </c>
       <c r="G3" t="n">
         <v>1.2048</v>
@@ -688,13 +688,13 @@
         <v>0.5498</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4048</v>
+        <v>0.8199</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5377</v>
+        <v>0.8786</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.133</v>
+        <v>-0.0586</v>
       </c>
       <c r="V3" t="n">
         <v>4.102</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5482</v>
+        <v>1.7861</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1372</v>
+        <v>3.9449</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.589</v>
+        <v>-2.1588</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9687</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8388</v>
+        <v>1.0767</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6214</v>
+        <v>0.4291</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2174</v>
+        <v>0.6476</v>
       </c>
       <c r="V4" t="n">
         <v>0.945</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ MERINO</t>
+          <t>J. SEGARRA SARIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2313</v>
+        <v>0.4009</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0234</v>
+        <v>1.1592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2547</v>
+        <v>-0.7583</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0546</v>
+        <v>0.4237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0867</v>
+        <v>0.7476</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0321</v>
+        <v>-0.3238</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0867</v>
+        <v>1.1871</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0867</v>
+        <v>1.062</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0321</v>
+        <v>-0.7633</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.3145</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0321</v>
+        <v>-0.4489</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1321</v>
+        <v>-0.2061</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1101</v>
+        <v>-0.0279</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2422</v>
+        <v>-0.1782</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SEGARRA SARIO</t>
+          <t>M. RODRIGUEZ MERINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0297</v>
+        <v>0.2779</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8821</v>
+        <v>0.2051</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4237</v>
+        <v>0.0546</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7476</v>
+        <v>0.0867</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3238</v>
+        <v>-0.0321</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1871</v>
+        <v>0.0867</v>
       </c>
       <c r="K6" t="n">
-        <v>1.062</v>
+        <v>0.0867</v>
       </c>
       <c r="L6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7633</v>
+        <v>-0.0321</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3145</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4489</v>
+        <v>-0.0321</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5773</v>
+        <v>0.1787</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2753</v>
+        <v>-0.0139</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.302</v>
+        <v>0.1927</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9083</v>
+        <v>-1.2749</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9695</v>
+        <v>2.7201</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.8778</v>
+        <v>-3.9949</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6327</v>
+        <v>-0.0548</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4176</v>
+        <v>-1.4559</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.215</v>
+        <v>1.401</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2002</v>
+        <v>3.7415</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3251</v>
+        <v>1.5389</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8752</v>
+        <v>2.2027</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.8329</v>
+        <v>-3.7964</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.7427</v>
+        <v>-2.9947</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0902</v>
+        <v>-0.8017</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0158</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0726</v>
+        <v>-0.0368</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4344</v>
+        <v>0.1776</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3619</v>
+        <v>-0.2144</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3324</v>
+        <v>-0.6335</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3324</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>M. ANTONI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1709</v>
+        <v>-2.2003</v>
       </c>
       <c r="E8" t="n">
-        <v>2.047</v>
+        <v>0.1263</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2179</v>
+        <v>-2.3266</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0548</v>
+        <v>-1.1744</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4559</v>
+        <v>0.4732</v>
       </c>
       <c r="I8" t="n">
-        <v>1.401</v>
+        <v>-1.6476</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7415</v>
+        <v>0.3277</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5389</v>
+        <v>2.1674</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2027</v>
+        <v>-1.8397</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7964</v>
+        <v>-1.5021</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.9947</v>
+        <v>-1.6943</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8017</v>
+        <v>0.1922</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5498</v>
+        <v>0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9328</v>
+        <v>0.6363</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4955</v>
+        <v>0.3929</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4373</v>
+        <v>0.2434</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6335</v>
+        <v>-2.212</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ANTONI RODRIGUEZ</t>
+          <t>S. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6156</v>
+        <v>-2.512</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.066</v>
+        <v>3.1067</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5496</v>
+        <v>-5.6188</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1744</v>
+        <v>0.5803</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4732</v>
+        <v>-1.1414</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6476</v>
+        <v>1.7217</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3277</v>
+        <v>5.0194</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1674</v>
+        <v>2.2075</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8397</v>
+        <v>2.8119</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5021</v>
+        <v>-4.4391</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6943</v>
+        <v>-3.3489</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1922</v>
+        <v>-1.0902</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5498</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>0.221</v>
+        <v>0.0963</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2006</v>
+        <v>0.4751</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0204</v>
+        <v>-0.3788</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.212</v>
+        <v>-0.6231</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3219</v>
+        <v>1.2774</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.5339</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. ARNAIZ VEGA</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9765</v>
+        <v>-2.8089</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6671</v>
+        <v>0.8707</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.6435</v>
+        <v>-3.6796</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5803</v>
+        <v>-1.6327</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1414</v>
+        <v>-1.4176</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7217</v>
+        <v>-0.215</v>
       </c>
       <c r="J10" t="n">
-        <v>5.0194</v>
+        <v>3.2002</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2075</v>
+        <v>2.3251</v>
       </c>
       <c r="L10" t="n">
-        <v>2.8119</v>
+        <v>0.8752</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.4391</v>
+        <v>-4.8329</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.3489</v>
+        <v>-3.7427</v>
       </c>
       <c r="O10" t="n">
         <v>-1.0902</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5656</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.6651</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3681</v>
+        <v>1.172</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0355</v>
+        <v>1.3356</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4036</v>
+        <v>-0.1637</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6231</v>
+        <v>-0.3324</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2774</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.9005</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3819</v>
+        <v>-3.7307</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9674</v>
+        <v>-1.242</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4144</v>
+        <v>-2.4887</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6438</v>
@@ -1312,13 +1312,13 @@
         <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8117</v>
+        <v>0.4629</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9517</v>
+        <v>0.6772</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1401</v>
+        <v>-0.2144</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8117</v>
+        <v>-4.2045</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8211</v>
+        <v>-3.1891</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9906</v>
+        <v>-1.0154</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6042</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0936</v>
+        <v>0.7008</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4404</v>
+        <v>0.1916</v>
       </c>
       <c r="U12" t="n">
-        <v>0.534</v>
+        <v>0.5092</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5681</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6280999999999999</v>
+        <v>1.178600000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>26.8722</v>
+        <v>27.4226</v>
       </c>
       <c r="F13" t="n">
-        <v>-26.2439</v>
+        <v>-26.2441</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3725</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.2646</v>
+        <v>-9.264600000000002</v>
       </c>
       <c r="I13" t="n">
         <v>6.892199999999999</v>
@@ -1468,22 +1468,22 @@
         <v>10.9954</v>
       </c>
       <c r="S13" t="n">
-        <v>5.0377</v>
+        <v>5.5881</v>
       </c>
       <c r="T13" t="n">
-        <v>4.3854</v>
+        <v>4.936</v>
       </c>
       <c r="U13" t="n">
         <v>0.6520999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5442</v>
+        <v>2.544200000000001</v>
       </c>
       <c r="W13" t="n">
         <v>11.4547</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.910500000000001</v>
+        <v>-8.910499999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2372</v>
+        <v>5.1045</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7228</v>
+        <v>8.011200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4856</v>
+        <v>-2.9067</v>
       </c>
       <c r="G14" t="n">
         <v>6.3899</v>
@@ -1546,13 +1546,13 @@
         <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6269</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8258</v>
+        <v>-0.5373</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1988</v>
+        <v>-0.2223</v>
       </c>
       <c r="V14" t="n">
         <v>0.3905</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7227</v>
+        <v>3.1865</v>
       </c>
       <c r="E15" t="n">
-        <v>5.148</v>
+        <v>4.8596</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4254</v>
+        <v>-1.6731</v>
       </c>
       <c r="G15" t="n">
         <v>1.7219</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7881</v>
+        <v>0.2519</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7866</v>
+        <v>0.4981</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0015</v>
+        <v>-0.2462</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2534</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7361</v>
+        <v>2.0027</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6091</v>
+        <v>0.8014</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1271</v>
+        <v>1.2014</v>
       </c>
       <c r="G16" t="n">
         <v>0.3563</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0862</v>
+        <v>-0.8196</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4404</v>
+        <v>-0.2481</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6458</v>
+        <v>-0.5715</v>
       </c>
       <c r="V16" t="n">
         <v>0.6335</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2127</v>
+        <v>1.5725</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1194</v>
+        <v>3.504</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9067</v>
+        <v>-1.9315</v>
       </c>
       <c r="G17" t="n">
         <v>-1.5145</v>
@@ -1780,13 +1780,13 @@
         <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5293</v>
+        <v>-0.1695</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3303</v>
+        <v>0.0543</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.199</v>
+        <v>-0.2238</v>
       </c>
       <c r="V17" t="n">
         <v>2.5235</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.173</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0157</v>
+        <v>0.7272</v>
       </c>
       <c r="F18" t="n">
         <v>0.1574</v>
@@ -1858,10 +1858,10 @@
         <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0732</v>
+        <v>-0.3616</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3658</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U18" t="n">
         <v>-0.4389</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5431</v>
+        <v>-0.7097</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2369</v>
+        <v>1.3005</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.78</v>
+        <v>-2.0102</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0434</v>
+        <v>1.1651</v>
       </c>
       <c r="H20" t="n">
-        <v>0.428</v>
+        <v>-0.2836</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4713</v>
+        <v>1.4488</v>
       </c>
       <c r="J20" t="n">
-        <v>0.761</v>
+        <v>4.2152</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6936</v>
+        <v>1.5481</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0674</v>
+        <v>2.6672</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8044</v>
+        <v>-3.0501</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2656</v>
+        <v>-1.8317</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5388</v>
+        <v>-1.2184</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1833</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1833</v>
+        <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>0.317</v>
+        <v>-0.5816</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4759</v>
+        <v>-0.1659</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1589</v>
+        <v>-0.4157</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2182</v>
+        <v>-0.9059</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9159</v>
+        <v>0.9484</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.134</v>
+        <v>-1.8543</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1651</v>
+        <v>-1.0434</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2836</v>
+        <v>0.428</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4488</v>
+        <v>-1.4713</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2152</v>
+        <v>0.761</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5481</v>
+        <v>0.6936</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6672</v>
+        <v>0.0674</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0501</v>
+        <v>-1.8044</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8317</v>
+        <v>-0.2656</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2184</v>
+        <v>-1.5388</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0901</v>
+        <v>-0.0458</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5505</v>
+        <v>0.1874</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5396</v>
+        <v>-0.2332</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. ROIG VALERO</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5821</v>
+        <v>-1.2921</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2073</v>
+        <v>1.9521</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7894</v>
+        <v>-3.2442</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1029</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0095</v>
+        <v>-1.3872</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1124</v>
+        <v>1.2983</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8786</v>
+        <v>3.2405</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4522</v>
+        <v>-0.0775</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5736</v>
+        <v>3.318</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9815</v>
+        <v>-3.3294</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4427</v>
+        <v>-1.3097</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5388</v>
+        <v>-2.0198</v>
       </c>
       <c r="P22" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6882</v>
+        <v>-0.4996</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0068</v>
+        <v>-0.3722</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3186</v>
+        <v>-0.1275</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9005</v>
+        <v>-0.8869</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2224</v>
+        <v>-0.8869</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>P. ROSELLO ORTS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7788</v>
+        <v>-2.0864</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6636</v>
+        <v>2.2071</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4424</v>
+        <v>-4.2935</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.8063</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3872</v>
+        <v>0.5114</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2983</v>
+        <v>-1.3177</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2405</v>
+        <v>1.7874</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0775</v>
+        <v>2.3034</v>
       </c>
       <c r="L23" t="n">
-        <v>3.318</v>
+        <v>-0.516</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3294</v>
+        <v>-2.5937</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3097</v>
+        <v>-1.792</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0198</v>
+        <v>-0.8017</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9863</v>
+        <v>-1.0577</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6606</v>
+        <v>-0.5645</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3256</v>
+        <v>-0.4932</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8869</v>
+        <v>-0.9554</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8869</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. ROSELLO ORTS</t>
+          <t>O. ROIG VALERO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0834</v>
+        <v>-2.156</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1109</v>
+        <v>1.5343</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1944</v>
+        <v>-3.6903</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8063</v>
+        <v>-1.1029</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5114</v>
+        <v>1.0095</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3177</v>
+        <v>-2.1124</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7874</v>
+        <v>0.8786</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3034</v>
+        <v>1.4522</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.516</v>
+        <v>-0.5736</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5937</v>
+        <v>-1.9815</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.792</v>
+        <v>-0.4427</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8017</v>
+        <v>-1.5388</v>
       </c>
       <c r="P24" t="n">
         <v>0.733</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6493</v>
+        <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0548</v>
+        <v>0.1143</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6606</v>
+        <v>0.3337</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3941</v>
+        <v>-0.2195</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9554</v>
+        <v>-1.9005</v>
       </c>
       <c r="W24" t="n">
-        <v>1.9005</v>
+        <v>0.3219</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8559</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8159</v>
+        <v>-2.9805</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4545</v>
+        <v>0.166</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2704</v>
+        <v>-3.1465</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1313</v>
@@ -2404,13 +2404,13 @@
         <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3201</v>
+        <v>0.1555</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.6082</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5766</v>
+        <v>-0.4527</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5545</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3386</v>
+        <v>-3.8985</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6566</v>
+        <v>0.8489</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.9952</v>
+        <v>-4.7475</v>
       </c>
       <c r="G26" t="n">
         <v>-1.2835</v>
@@ -2482,13 +2482,13 @@
         <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.7044</v>
+        <v>-1.2643</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7157</v>
+        <v>-0.5234</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9887</v>
+        <v>-0.741</v>
       </c>
       <c r="V26" t="n">
         <v>-1.9005</v>
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6282000000000014</v>
+        <v>-0.6281000000000003</v>
       </c>
       <c r="E27" t="n">
         <v>27.5109</v>
@@ -2524,13 +2524,13 @@
         <v>-28.139</v>
       </c>
       <c r="G27" t="n">
-        <v>2.372400000000001</v>
+        <v>2.3724</v>
       </c>
       <c r="H27" t="n">
-        <v>9.264699999999998</v>
+        <v>9.264699999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-6.892199999999999</v>
+        <v>-6.8922</v>
       </c>
       <c r="J27" t="n">
         <v>28.981</v>
@@ -2539,10 +2539,10 @@
         <v>21.7663</v>
       </c>
       <c r="L27" t="n">
-        <v>7.2149</v>
+        <v>7.214899999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-26.6087</v>
+        <v>-26.60870000000001</v>
       </c>
       <c r="N27" t="n">
         <v>-12.5017</v>
@@ -2560,10 +2560,10 @@
         <v>15.577</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.0378</v>
+        <v>-5.037599999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6520999999999999</v>
+        <v>-0.6524</v>
       </c>
       <c r="U27" t="n">
         <v>-4.3855</v>
